--- a/Result/profitability/2616.xlsx
+++ b/Result/profitability/2616.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.34</v>
+        <v>-1.28</v>
       </c>
       <c r="N2" t="n">
-        <v>6.668749999999999</v>
+        <v>6.7025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0575</v>
+        <v>-1.0025</v>
       </c>
       <c r="N3" t="n">
-        <v>6.91625</v>
+        <v>7.034999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8</v>
+        <v>-0.765</v>
       </c>
       <c r="N4" t="n">
-        <v>7.22375</v>
+        <v>7.11375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5975</v>
+        <v>-0.58</v>
       </c>
       <c r="N5" t="n">
-        <v>7.422499999999999</v>
+        <v>7.32375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4</v>
+        <v>-0.37375</v>
       </c>
       <c r="N6" t="n">
-        <v>7.757499999999999</v>
+        <v>7.65375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.16</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.08</v>
+        <v>7.87125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.48</v>
       </c>
       <c r="M8" t="n">
-        <v>0.13</v>
+        <v>0.14375</v>
       </c>
       <c r="N8" t="n">
-        <v>8.14875</v>
+        <v>7.9625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.3525</v>
       </c>
       <c r="N9" t="n">
-        <v>8.202500000000001</v>
+        <v>8.202499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.36375</v>
       </c>
       <c r="N10" t="n">
-        <v>8.171250000000001</v>
+        <v>8.171249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.4425</v>
       </c>
       <c r="N13" t="n">
-        <v>8.008750000000001</v>
+        <v>8.008749999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2388</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2247</v>
+      </c>
+      <c r="E75" t="n">
+        <v>140</v>
+      </c>
+      <c r="F75" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-176</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-7.38%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>18</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-158</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-172</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="N75" t="n">
+        <v>6.435</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.08029197080291972</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2021709633649933</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09999999999999998</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1184407796101949</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
